--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-dmi-discriminator.xlsx
+++ b/main/ig/CodeSystem-dmi-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
